--- a/datos/Machote_Tarifas_CECYTEA_V3.xlsx
+++ b/datos/Machote_Tarifas_CECYTEA_V3.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaime.villalobos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4505F399-A7E4-406A-A498-FE441CE87DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21058E19-9B11-4EC0-AE5B-D0094CF1EFA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
     <sheet name="PLANTELES" sheetId="2" r:id="rId2"/>
     <sheet name="TARIFAS" sheetId="3" r:id="rId3"/>
     <sheet name="SALDOS_INICIALES" sheetId="4" r:id="rId4"/>
-    <sheet name="REFERENCIA_ORIGINAL" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="96">
   <si>
     <t>MACHOTE DE TARIFAS · SISTEMA DE TIENDAS ESCOLARES CECyTEA · V3</t>
   </si>
@@ -67,9 +66,6 @@
     <t>4. PAGOS</t>
   </si>
   <si>
-    <t>El sistema tomará solo los movimientos de GLOBAL cuyo Nombre(s) contenga la palabra TIEND. Separará cada depósito entre Cuota y EE.</t>
-  </si>
-  <si>
     <t>5. FIFO Y PARCIALES</t>
   </si>
   <si>
@@ -112,9 +108,6 @@
     <t>CATÁLOGO DE PLANTELES</t>
   </si>
   <si>
-    <t>Completa las claves vacías antes de usar esos planteles en el sistema. Las claves ya incluidas se tomaron del archivo de tarifas entregado.</t>
-  </si>
-  <si>
     <t>CLAVE_PLANTEL</t>
   </si>
   <si>
@@ -319,48 +312,6 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>REFERENCIA DEL ARCHIVO DE TARIFAS ORIGINAL</t>
-  </si>
-  <si>
-    <t>Esta hoja conserva la estructura y montos de tarifas_base(2).xlsx como referencia. El nuevo sistema utilizará la hoja TARIFAS, no esta hoja.</t>
-  </si>
-  <si>
-    <t>PLANTEL</t>
-  </si>
-  <si>
-    <t>CLAVE</t>
-  </si>
-  <si>
-    <t>FEB-26 CUOTA</t>
-  </si>
-  <si>
-    <t>FEB-26 EE</t>
-  </si>
-  <si>
-    <t>MAR-26 CUOTA</t>
-  </si>
-  <si>
-    <t>MAR-26 EE</t>
-  </si>
-  <si>
-    <t>ABR-26 CUOTA</t>
-  </si>
-  <si>
-    <t>ABR-26 EE</t>
-  </si>
-  <si>
-    <t>MAY-26 CUOTA</t>
-  </si>
-  <si>
-    <t>MAY-26 EE</t>
-  </si>
-  <si>
-    <t>JUN-26 CUOTA</t>
-  </si>
-  <si>
-    <t>JUN-26 EE</t>
-  </si>
-  <si>
     <t>ACTIVA</t>
   </si>
   <si>
@@ -368,6 +319,12 @@
   </si>
   <si>
     <t>ESTATUS_TIENDA</t>
+  </si>
+  <si>
+    <t>El sistema tomará solo los movimientos de GLOBAL cuyo Nombre(s) contenga la palabra TIENDA. Separará cada depósito entre Cuota y EE.</t>
+  </si>
+  <si>
+    <t>Completa las claves vacías antes de usar esos planteles en el sistema.</t>
   </si>
 </sst>
 </file>
@@ -738,36 +695,36 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45.95" customHeight="1">
       <c r="A9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45.95" customHeight="1">
       <c r="A10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45.95" customHeight="1">
       <c r="A11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
       <c r="A13" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -777,15 +734,15 @@
     </row>
     <row r="14" spans="1:6" ht="15">
       <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1">
         <v>32</v>
@@ -793,7 +750,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1">
         <v>5</v>
@@ -801,10 +758,10 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -830,7 +787,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -838,7 +795,7 @@
     </row>
     <row r="2" spans="1:4" ht="15">
       <c r="A2" s="12" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -846,442 +803,442 @@
     </row>
     <row r="3" spans="1:4" ht="15">
       <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1307,7 +1264,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="27.95" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1318,7 +1275,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -1329,33 +1286,33 @@
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="5">
         <v>46054</v>
@@ -1371,15 +1328,15 @@
         <v>2186</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5">
         <v>46082</v>
@@ -1395,15 +1352,15 @@
         <v>4372</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C6" s="5">
         <v>46113</v>
@@ -1419,15 +1376,15 @@
         <v>2186</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5">
         <v>46143</v>
@@ -1443,15 +1400,15 @@
         <v>4372</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5">
         <v>46174</v>
@@ -1467,15 +1424,15 @@
         <v>4372</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5">
         <v>46054</v>
@@ -1491,15 +1448,15 @@
         <v>4025</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5">
         <v>46082</v>
@@ -1515,15 +1472,15 @@
         <v>8050</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="5">
         <v>46113</v>
@@ -1539,15 +1496,15 @@
         <v>4025</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="5">
         <v>46143</v>
@@ -1563,15 +1520,15 @@
         <v>8050</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="5">
         <v>46174</v>
@@ -1587,15 +1544,15 @@
         <v>8050</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="5">
         <v>46054</v>
@@ -1611,15 +1568,15 @@
         <v>4786</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" s="5">
         <v>46082</v>
@@ -1635,15 +1592,15 @@
         <v>9571</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="5">
         <v>46113</v>
@@ -1659,15 +1616,15 @@
         <v>4786</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17" s="5">
         <v>46143</v>
@@ -1683,15 +1640,15 @@
         <v>9571</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C18" s="5">
         <v>46174</v>
@@ -1707,15 +1664,15 @@
         <v>9571</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" s="5">
         <v>46054</v>
@@ -1731,15 +1688,15 @@
         <v>5471</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C20" s="5">
         <v>46082</v>
@@ -1755,15 +1712,15 @@
         <v>10941</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C21" s="5">
         <v>46113</v>
@@ -1779,15 +1736,15 @@
         <v>5471</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C22" s="5">
         <v>46143</v>
@@ -1803,15 +1760,15 @@
         <v>10941</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5">
         <v>46174</v>
@@ -1827,15 +1784,15 @@
         <v>10941</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C24" s="5">
         <v>46054</v>
@@ -1851,15 +1808,15 @@
         <v>4786</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C25" s="5">
         <v>46082</v>
@@ -1875,15 +1832,15 @@
         <v>9571</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C26" s="5">
         <v>46113</v>
@@ -1899,15 +1856,15 @@
         <v>4786</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C27" s="5">
         <v>46143</v>
@@ -1923,15 +1880,15 @@
         <v>9571</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C28" s="5">
         <v>46174</v>
@@ -1947,15 +1904,15 @@
         <v>9571</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C29" s="5">
         <v>46054</v>
@@ -1971,15 +1928,15 @@
         <v>5471</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="5">
         <v>46082</v>
@@ -1995,15 +1952,15 @@
         <v>10941</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C31" s="5">
         <v>46113</v>
@@ -2019,15 +1976,15 @@
         <v>5471</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C32" s="5">
         <v>46143</v>
@@ -2043,15 +2000,15 @@
         <v>10941</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C33" s="5">
         <v>46174</v>
@@ -2067,15 +2024,15 @@
         <v>10941</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C34" s="5">
         <v>46054</v>
@@ -2091,15 +2048,15 @@
         <v>2186</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C35" s="5">
         <v>46082</v>
@@ -2115,15 +2072,15 @@
         <v>4372</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C36" s="5">
         <v>46113</v>
@@ -2139,15 +2096,15 @@
         <v>2186</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C37" s="5">
         <v>46143</v>
@@ -2163,15 +2120,15 @@
         <v>4372</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C38" s="5">
         <v>46174</v>
@@ -2187,15 +2144,15 @@
         <v>4372</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C39" s="5">
         <v>46054</v>
@@ -2211,15 +2168,15 @@
         <v>315</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C40" s="5">
         <v>46082</v>
@@ -2235,15 +2192,15 @@
         <v>630</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C41" s="5">
         <v>46113</v>
@@ -2259,15 +2216,15 @@
         <v>315</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C42" s="5">
         <v>46143</v>
@@ -2283,15 +2240,15 @@
         <v>630</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C43" s="5">
         <v>46174</v>
@@ -2307,15 +2264,15 @@
         <v>630</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C44" s="5">
         <v>46054</v>
@@ -2331,15 +2288,15 @@
         <v>1955</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C45" s="5">
         <v>46082</v>
@@ -2355,15 +2312,15 @@
         <v>3911</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C46" s="5">
         <v>46113</v>
@@ -2379,15 +2336,15 @@
         <v>1955</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C47" s="5">
         <v>46143</v>
@@ -2403,15 +2360,15 @@
         <v>3911</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C48" s="5">
         <v>46174</v>
@@ -2427,15 +2384,15 @@
         <v>3911</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C49" s="5">
         <v>46054</v>
@@ -2451,15 +2408,15 @@
         <v>4236</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C50" s="5">
         <v>46082</v>
@@ -2475,15 +2432,15 @@
         <v>8473</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C51" s="5">
         <v>46113</v>
@@ -2499,15 +2456,15 @@
         <v>4236</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C52" s="5">
         <v>46143</v>
@@ -2523,15 +2480,15 @@
         <v>8473</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C53" s="5">
         <v>46174</v>
@@ -2547,15 +2504,15 @@
         <v>8473</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C54" s="5">
         <v>46054</v>
@@ -2571,15 +2528,15 @@
         <v>3141</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C55" s="5">
         <v>46082</v>
@@ -2595,15 +2552,15 @@
         <v>6282</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C56" s="5">
         <v>46113</v>
@@ -2619,15 +2576,15 @@
         <v>3141</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C57" s="5">
         <v>46143</v>
@@ -2643,15 +2600,15 @@
         <v>6282</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C58" s="5">
         <v>46174</v>
@@ -2667,15 +2624,15 @@
         <v>6282</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C59" s="5">
         <v>46054</v>
@@ -2691,15 +2648,15 @@
         <v>4236</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C60" s="5">
         <v>46082</v>
@@ -2715,15 +2672,15 @@
         <v>8473</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C61" s="5">
         <v>46113</v>
@@ -2739,15 +2696,15 @@
         <v>4236</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C62" s="5">
         <v>46143</v>
@@ -2763,15 +2720,15 @@
         <v>8473</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="5">
         <v>46174</v>
@@ -2787,15 +2744,15 @@
         <v>8473</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C64" s="5">
         <v>46054</v>
@@ -2811,15 +2768,15 @@
         <v>2186</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C65" s="5">
         <v>46082</v>
@@ -2835,15 +2792,15 @@
         <v>4372</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C66" s="5">
         <v>46113</v>
@@ -2859,15 +2816,15 @@
         <v>2186</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C67" s="5">
         <v>46143</v>
@@ -2883,15 +2840,15 @@
         <v>4372</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C68" s="5">
         <v>46174</v>
@@ -2907,15 +2864,15 @@
         <v>4372</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C69" s="5">
         <v>46054</v>
@@ -2931,15 +2888,15 @@
         <v>315</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C70" s="5">
         <v>46082</v>
@@ -2955,15 +2912,15 @@
         <v>630</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C71" s="5">
         <v>46113</v>
@@ -2979,15 +2936,15 @@
         <v>315</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C72" s="5">
         <v>46143</v>
@@ -3003,15 +2960,15 @@
         <v>630</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C73" s="5">
         <v>46174</v>
@@ -3027,15 +2984,15 @@
         <v>630</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C74" s="5">
         <v>46054</v>
@@ -3051,15 +3008,15 @@
         <v>2186</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C75" s="5">
         <v>46082</v>
@@ -3075,15 +3032,15 @@
         <v>4372</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C76" s="5">
         <v>46113</v>
@@ -3099,15 +3056,15 @@
         <v>2186</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C77" s="5">
         <v>46143</v>
@@ -3123,15 +3080,15 @@
         <v>4372</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C78" s="5">
         <v>46174</v>
@@ -3147,15 +3104,15 @@
         <v>4372</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C79" s="5">
         <v>46054</v>
@@ -3171,15 +3128,15 @@
         <v>168</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C80" s="5">
         <v>46082</v>
@@ -3195,15 +3152,15 @@
         <v>335</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C81" s="5">
         <v>46113</v>
@@ -3219,15 +3176,15 @@
         <v>168</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C82" s="5">
         <v>46143</v>
@@ -3243,15 +3200,15 @@
         <v>335</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C83" s="5">
         <v>46174</v>
@@ -3267,13 +3224,13 @@
         <v>335</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="3"/>
       <c r="B84" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C84" s="5">
         <v>46054</v>
@@ -3289,13 +3246,13 @@
         <v>0</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="3"/>
       <c r="B85" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C85" s="5">
         <v>46082</v>
@@ -3311,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="3"/>
       <c r="B86" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C86" s="5">
         <v>46113</v>
@@ -3333,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="3"/>
       <c r="B87" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C87" s="5">
         <v>46143</v>
@@ -3355,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="3"/>
       <c r="B88" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C88" s="5">
         <v>46174</v>
@@ -3377,15 +3334,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C89" s="5">
         <v>46054</v>
@@ -3401,15 +3358,15 @@
         <v>168</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C90" s="5">
         <v>46082</v>
@@ -3425,15 +3382,15 @@
         <v>335</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C91" s="5">
         <v>46113</v>
@@ -3449,15 +3406,15 @@
         <v>168</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C92" s="5">
         <v>46143</v>
@@ -3473,15 +3430,15 @@
         <v>335</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C93" s="5">
         <v>46174</v>
@@ -3497,15 +3454,15 @@
         <v>335</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C94" s="5">
         <v>46054</v>
@@ -3521,15 +3478,15 @@
         <v>168</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C95" s="5">
         <v>46082</v>
@@ -3545,15 +3502,15 @@
         <v>335</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C96" s="5">
         <v>46113</v>
@@ -3569,15 +3526,15 @@
         <v>168</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C97" s="5">
         <v>46143</v>
@@ -3593,15 +3550,15 @@
         <v>335</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C98" s="5">
         <v>46174</v>
@@ -3617,15 +3574,15 @@
         <v>335</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C99" s="5">
         <v>46054</v>
@@ -3641,15 +3598,15 @@
         <v>168</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C100" s="5">
         <v>46082</v>
@@ -3665,15 +3622,15 @@
         <v>335</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C101" s="5">
         <v>46113</v>
@@ -3689,15 +3646,15 @@
         <v>168</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C102" s="5">
         <v>46143</v>
@@ -3713,15 +3670,15 @@
         <v>335</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C103" s="5">
         <v>46174</v>
@@ -3737,15 +3694,15 @@
         <v>335</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C104" s="5">
         <v>46054</v>
@@ -3761,15 +3718,15 @@
         <v>110</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C105" s="5">
         <v>46082</v>
@@ -3785,15 +3742,15 @@
         <v>220</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C106" s="5">
         <v>46113</v>
@@ -3809,15 +3766,15 @@
         <v>110</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C107" s="5">
         <v>46143</v>
@@ -3833,15 +3790,15 @@
         <v>220</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C108" s="5">
         <v>46174</v>
@@ -3857,13 +3814,13 @@
         <v>220</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="3"/>
       <c r="B109" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C109" s="5">
         <v>46054</v>
@@ -3879,13 +3836,13 @@
         <v>0</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="3"/>
       <c r="B110" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C110" s="5">
         <v>46082</v>
@@ -3901,13 +3858,13 @@
         <v>0</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="3"/>
       <c r="B111" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C111" s="5">
         <v>46113</v>
@@ -3923,13 +3880,13 @@
         <v>0</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="3"/>
       <c r="B112" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C112" s="5">
         <v>46143</v>
@@ -3945,13 +3902,13 @@
         <v>0</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="3"/>
       <c r="B113" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C113" s="5">
         <v>46174</v>
@@ -3967,13 +3924,13 @@
         <v>0</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="3"/>
       <c r="B114" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C114" s="5">
         <v>46054</v>
@@ -3989,13 +3946,13 @@
         <v>0</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="3"/>
       <c r="B115" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C115" s="5">
         <v>46082</v>
@@ -4011,13 +3968,13 @@
         <v>0</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="3"/>
       <c r="B116" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C116" s="5">
         <v>46113</v>
@@ -4033,13 +3990,13 @@
         <v>0</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="3"/>
       <c r="B117" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C117" s="5">
         <v>46143</v>
@@ -4055,13 +4012,13 @@
         <v>0</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="3"/>
       <c r="B118" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C118" s="5">
         <v>46174</v>
@@ -4077,13 +4034,13 @@
         <v>0</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="3"/>
       <c r="B119" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C119" s="5">
         <v>46054</v>
@@ -4099,13 +4056,13 @@
         <v>0</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="3"/>
       <c r="B120" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C120" s="5">
         <v>46082</v>
@@ -4121,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="3"/>
       <c r="B121" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C121" s="5">
         <v>46113</v>
@@ -4143,13 +4100,13 @@
         <v>0</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="3"/>
       <c r="B122" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C122" s="5">
         <v>46143</v>
@@ -4165,13 +4122,13 @@
         <v>0</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="3"/>
       <c r="B123" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C123" s="5">
         <v>46174</v>
@@ -4187,13 +4144,13 @@
         <v>0</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="3"/>
       <c r="B124" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C124" s="5">
         <v>46054</v>
@@ -4209,13 +4166,13 @@
         <v>0</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="3"/>
       <c r="B125" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C125" s="5">
         <v>46082</v>
@@ -4231,13 +4188,13 @@
         <v>0</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="3"/>
       <c r="B126" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C126" s="5">
         <v>46113</v>
@@ -4253,13 +4210,13 @@
         <v>0</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="3"/>
       <c r="B127" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C127" s="5">
         <v>46143</v>
@@ -4275,13 +4232,13 @@
         <v>0</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="3"/>
       <c r="B128" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C128" s="5">
         <v>46174</v>
@@ -4297,13 +4254,13 @@
         <v>0</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="3"/>
       <c r="B129" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C129" s="5">
         <v>46054</v>
@@ -4319,13 +4276,13 @@
         <v>0</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="3"/>
       <c r="B130" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C130" s="5">
         <v>46082</v>
@@ -4341,13 +4298,13 @@
         <v>0</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="3"/>
       <c r="B131" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C131" s="5">
         <v>46113</v>
@@ -4363,13 +4320,13 @@
         <v>0</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="3"/>
       <c r="B132" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C132" s="5">
         <v>46143</v>
@@ -4385,13 +4342,13 @@
         <v>0</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="3"/>
       <c r="B133" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C133" s="5">
         <v>46174</v>
@@ -4407,13 +4364,13 @@
         <v>0</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="3"/>
       <c r="B134" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C134" s="5">
         <v>46054</v>
@@ -4429,13 +4386,13 @@
         <v>0</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="3"/>
       <c r="B135" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C135" s="5">
         <v>46082</v>
@@ -4451,13 +4408,13 @@
         <v>0</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="3"/>
       <c r="B136" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C136" s="5">
         <v>46113</v>
@@ -4473,13 +4430,13 @@
         <v>0</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="3"/>
       <c r="B137" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C137" s="5">
         <v>46143</v>
@@ -4495,13 +4452,13 @@
         <v>0</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="3"/>
       <c r="B138" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C138" s="5">
         <v>46174</v>
@@ -4517,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="3"/>
       <c r="B139" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C139" s="5">
         <v>46054</v>
@@ -4539,13 +4496,13 @@
         <v>0</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="3"/>
       <c r="B140" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C140" s="5">
         <v>46082</v>
@@ -4561,13 +4518,13 @@
         <v>0</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="3"/>
       <c r="B141" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C141" s="5">
         <v>46113</v>
@@ -4583,13 +4540,13 @@
         <v>0</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="3"/>
       <c r="B142" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C142" s="5">
         <v>46143</v>
@@ -4605,13 +4562,13 @@
         <v>0</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="3"/>
       <c r="B143" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C143" s="5">
         <v>46174</v>
@@ -4627,13 +4584,13 @@
         <v>0</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="3"/>
       <c r="B144" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C144" s="5">
         <v>46054</v>
@@ -4649,13 +4606,13 @@
         <v>0</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="3"/>
       <c r="B145" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C145" s="5">
         <v>46082</v>
@@ -4671,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="3"/>
       <c r="B146" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C146" s="5">
         <v>46113</v>
@@ -4693,13 +4650,13 @@
         <v>0</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="3"/>
       <c r="B147" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C147" s="5">
         <v>46143</v>
@@ -4715,13 +4672,13 @@
         <v>0</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="3"/>
       <c r="B148" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C148" s="5">
         <v>46174</v>
@@ -4737,13 +4694,13 @@
         <v>0</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="3"/>
       <c r="B149" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C149" s="5">
         <v>46054</v>
@@ -4759,13 +4716,13 @@
         <v>0</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="3"/>
       <c r="B150" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C150" s="5">
         <v>46082</v>
@@ -4781,13 +4738,13 @@
         <v>0</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="3"/>
       <c r="B151" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C151" s="5">
         <v>46113</v>
@@ -4803,13 +4760,13 @@
         <v>0</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="3"/>
       <c r="B152" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C152" s="5">
         <v>46143</v>
@@ -4825,13 +4782,13 @@
         <v>0</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="3"/>
       <c r="B153" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C153" s="5">
         <v>46174</v>
@@ -4847,13 +4804,13 @@
         <v>0</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="3"/>
       <c r="B154" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C154" s="5">
         <v>46054</v>
@@ -4869,13 +4826,13 @@
         <v>0</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="3"/>
       <c r="B155" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C155" s="5">
         <v>46082</v>
@@ -4891,13 +4848,13 @@
         <v>0</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="3"/>
       <c r="B156" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C156" s="5">
         <v>46113</v>
@@ -4913,13 +4870,13 @@
         <v>0</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="3"/>
       <c r="B157" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C157" s="5">
         <v>46143</v>
@@ -4935,13 +4892,13 @@
         <v>0</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="3"/>
       <c r="B158" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C158" s="5">
         <v>46174</v>
@@ -4957,15 +4914,15 @@
         <v>0</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C159" s="5">
         <v>46054</v>
@@ -4981,15 +4938,15 @@
         <v>168</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C160" s="5">
         <v>46082</v>
@@ -5005,15 +4962,15 @@
         <v>335</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C161" s="5">
         <v>46113</v>
@@ -5029,15 +4986,15 @@
         <v>168</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C162" s="5">
         <v>46143</v>
@@ -5053,15 +5010,15 @@
         <v>335</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C163" s="5">
         <v>46174</v>
@@ -5077,7 +5034,7 @@
         <v>335</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5102,7 +5059,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5111,7 +5068,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -5120,27 +5077,27 @@
     </row>
     <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="6">
         <v>0</v>
@@ -5152,10 +5109,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6">
         <v>0</v>
@@ -5167,10 +5124,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="6">
         <v>0</v>
@@ -5182,10 +5139,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="6">
         <v>0</v>
@@ -5197,10 +5154,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8" s="6">
         <v>0</v>
@@ -5212,10 +5169,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" s="6">
         <v>0</v>
@@ -5227,10 +5184,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6">
         <v>0</v>
@@ -5242,10 +5199,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" s="6">
         <v>0</v>
@@ -5257,10 +5214,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" s="6">
         <v>0</v>
@@ -5272,10 +5229,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C13" s="6">
         <v>0</v>
@@ -5287,10 +5244,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="6">
         <v>0</v>
@@ -5302,10 +5259,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C15" s="6">
         <v>0</v>
@@ -5317,10 +5274,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C16" s="6">
         <v>0</v>
@@ -5332,10 +5289,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C17" s="6">
         <v>0</v>
@@ -5347,10 +5304,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="6">
         <v>0</v>
@@ -5362,10 +5319,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19" s="6">
         <v>0</v>
@@ -5378,7 +5335,7 @@
     <row r="20" spans="1:5">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C20" s="6">
         <v>0</v>
@@ -5390,10 +5347,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C21" s="6">
         <v>0</v>
@@ -5405,10 +5362,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C22" s="6">
         <v>0</v>
@@ -5420,10 +5377,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C23" s="6">
         <v>0</v>
@@ -5435,10 +5392,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C24" s="6">
         <v>0</v>
@@ -5451,7 +5408,7 @@
     <row r="25" spans="1:5">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="6">
         <v>0</v>
@@ -5464,7 +5421,7 @@
     <row r="26" spans="1:5">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" s="6">
         <v>0</v>
@@ -5477,7 +5434,7 @@
     <row r="27" spans="1:5">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" s="6">
         <v>0</v>
@@ -5490,7 +5447,7 @@
     <row r="28" spans="1:5">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C28" s="6">
         <v>0</v>
@@ -5503,7 +5460,7 @@
     <row r="29" spans="1:5">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C29" s="6">
         <v>0</v>
@@ -5516,7 +5473,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" s="6">
         <v>0</v>
@@ -5529,7 +5486,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C31" s="6">
         <v>0</v>
@@ -5542,7 +5499,7 @@
     <row r="32" spans="1:5">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C32" s="6">
         <v>0</v>
@@ -5555,7 +5512,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C33" s="6">
         <v>0</v>
@@ -5568,7 +5525,7 @@
     <row r="34" spans="1:5">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" s="6">
         <v>0</v>
@@ -5580,10 +5537,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C35" s="6">
         <v>0</v>
@@ -5600,1286 +5557,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="12" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="27.95" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-    </row>
-    <row r="3" spans="1:12" ht="30">
-      <c r="A3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="6">
-        <v>1840</v>
-      </c>
-      <c r="D4" s="6">
-        <v>346</v>
-      </c>
-      <c r="E4" s="6">
-        <v>3680</v>
-      </c>
-      <c r="F4" s="6">
-        <v>692</v>
-      </c>
-      <c r="G4" s="6">
-        <v>1840</v>
-      </c>
-      <c r="H4" s="6">
-        <v>346</v>
-      </c>
-      <c r="I4" s="6">
-        <v>3680</v>
-      </c>
-      <c r="J4" s="6">
-        <v>692</v>
-      </c>
-      <c r="K4" s="6">
-        <v>3680</v>
-      </c>
-      <c r="L4" s="6">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="6">
-        <v>4025</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>8050</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>4025</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <v>8050</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>8050</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="6">
-        <v>4025</v>
-      </c>
-      <c r="D6" s="6">
-        <v>761</v>
-      </c>
-      <c r="E6" s="6">
-        <v>8050</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1521</v>
-      </c>
-      <c r="G6" s="6">
-        <v>4025</v>
-      </c>
-      <c r="H6" s="6">
-        <v>761</v>
-      </c>
-      <c r="I6" s="6">
-        <v>8050</v>
-      </c>
-      <c r="J6" s="6">
-        <v>1521</v>
-      </c>
-      <c r="K6" s="6">
-        <v>8050</v>
-      </c>
-      <c r="L6" s="6">
-        <v>1521</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="6">
-        <v>4600</v>
-      </c>
-      <c r="D7" s="6">
-        <v>871</v>
-      </c>
-      <c r="E7" s="6">
-        <v>9200</v>
-      </c>
-      <c r="F7" s="6">
-        <v>1741</v>
-      </c>
-      <c r="G7" s="6">
-        <v>4600</v>
-      </c>
-      <c r="H7" s="6">
-        <v>871</v>
-      </c>
-      <c r="I7" s="6">
-        <v>9200</v>
-      </c>
-      <c r="J7" s="6">
-        <v>1741</v>
-      </c>
-      <c r="K7" s="6">
-        <v>9200</v>
-      </c>
-      <c r="L7" s="6">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="6">
-        <v>4025</v>
-      </c>
-      <c r="D8" s="6">
-        <v>761</v>
-      </c>
-      <c r="E8" s="6">
-        <v>8050</v>
-      </c>
-      <c r="F8" s="6">
-        <v>1521</v>
-      </c>
-      <c r="G8" s="6">
-        <v>4025</v>
-      </c>
-      <c r="H8" s="6">
-        <v>761</v>
-      </c>
-      <c r="I8" s="6">
-        <v>8050</v>
-      </c>
-      <c r="J8" s="6">
-        <v>1521</v>
-      </c>
-      <c r="K8" s="6">
-        <v>8050</v>
-      </c>
-      <c r="L8" s="6">
-        <v>1521</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="6">
-        <v>4600</v>
-      </c>
-      <c r="D9" s="6">
-        <v>871</v>
-      </c>
-      <c r="E9" s="6">
-        <v>9200</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1741</v>
-      </c>
-      <c r="G9" s="6">
-        <v>4600</v>
-      </c>
-      <c r="H9" s="6">
-        <v>871</v>
-      </c>
-      <c r="I9" s="6">
-        <v>9200</v>
-      </c>
-      <c r="J9" s="6">
-        <v>1741</v>
-      </c>
-      <c r="K9" s="6">
-        <v>9200</v>
-      </c>
-      <c r="L9" s="6">
-        <v>1741</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1840</v>
-      </c>
-      <c r="D10" s="6">
-        <v>346</v>
-      </c>
-      <c r="E10" s="6">
-        <v>3680</v>
-      </c>
-      <c r="F10" s="6">
-        <v>692</v>
-      </c>
-      <c r="G10" s="6">
-        <v>1840</v>
-      </c>
-      <c r="H10" s="6">
-        <v>346</v>
-      </c>
-      <c r="I10" s="6">
-        <v>3680</v>
-      </c>
-      <c r="J10" s="6">
-        <v>692</v>
-      </c>
-      <c r="K10" s="6">
-        <v>3680</v>
-      </c>
-      <c r="L10" s="6">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="6">
-        <v>265</v>
-      </c>
-      <c r="D11" s="6">
-        <v>50</v>
-      </c>
-      <c r="E11" s="6">
-        <v>530</v>
-      </c>
-      <c r="F11" s="6">
-        <v>100</v>
-      </c>
-      <c r="G11" s="6">
-        <v>265</v>
-      </c>
-      <c r="H11" s="6">
-        <v>50</v>
-      </c>
-      <c r="I11" s="6">
-        <v>530</v>
-      </c>
-      <c r="J11" s="6">
-        <v>100</v>
-      </c>
-      <c r="K11" s="6">
-        <v>530</v>
-      </c>
-      <c r="L11" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1840</v>
-      </c>
-      <c r="D12" s="6">
-        <v>115</v>
-      </c>
-      <c r="E12" s="6">
-        <v>3680</v>
-      </c>
-      <c r="F12" s="6">
-        <v>231</v>
-      </c>
-      <c r="G12" s="6">
-        <v>1840</v>
-      </c>
-      <c r="H12" s="6">
-        <v>115</v>
-      </c>
-      <c r="I12" s="6">
-        <v>3680</v>
-      </c>
-      <c r="J12" s="6">
-        <v>231</v>
-      </c>
-      <c r="K12" s="6">
-        <v>3680</v>
-      </c>
-      <c r="L12" s="6">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="6">
-        <v>3565</v>
-      </c>
-      <c r="D13" s="6">
-        <v>671</v>
-      </c>
-      <c r="E13" s="6">
-        <v>7130</v>
-      </c>
-      <c r="F13" s="6">
-        <v>1343</v>
-      </c>
-      <c r="G13" s="6">
-        <v>3565</v>
-      </c>
-      <c r="H13" s="6">
-        <v>671</v>
-      </c>
-      <c r="I13" s="6">
-        <v>7130</v>
-      </c>
-      <c r="J13" s="6">
-        <v>1343</v>
-      </c>
-      <c r="K13" s="6">
-        <v>7130</v>
-      </c>
-      <c r="L13" s="6">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2643</v>
-      </c>
-      <c r="D14" s="6">
-        <v>498</v>
-      </c>
-      <c r="E14" s="6">
-        <v>5285</v>
-      </c>
-      <c r="F14" s="6">
-        <v>997</v>
-      </c>
-      <c r="G14" s="6">
-        <v>2643</v>
-      </c>
-      <c r="H14" s="6">
-        <v>498</v>
-      </c>
-      <c r="I14" s="6">
-        <v>5285</v>
-      </c>
-      <c r="J14" s="6">
-        <v>997</v>
-      </c>
-      <c r="K14" s="6">
-        <v>5285</v>
-      </c>
-      <c r="L14" s="6">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="6">
-        <v>3565</v>
-      </c>
-      <c r="D15" s="6">
-        <v>671</v>
-      </c>
-      <c r="E15" s="6">
-        <v>7130</v>
-      </c>
-      <c r="F15" s="6">
-        <v>1343</v>
-      </c>
-      <c r="G15" s="6">
-        <v>3565</v>
-      </c>
-      <c r="H15" s="6">
-        <v>671</v>
-      </c>
-      <c r="I15" s="6">
-        <v>7130</v>
-      </c>
-      <c r="J15" s="6">
-        <v>1343</v>
-      </c>
-      <c r="K15" s="6">
-        <v>7130</v>
-      </c>
-      <c r="L15" s="6">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1840</v>
-      </c>
-      <c r="D16" s="6">
-        <v>346</v>
-      </c>
-      <c r="E16" s="6">
-        <v>3680</v>
-      </c>
-      <c r="F16" s="6">
-        <v>692</v>
-      </c>
-      <c r="G16" s="6">
-        <v>1840</v>
-      </c>
-      <c r="H16" s="6">
-        <v>346</v>
-      </c>
-      <c r="I16" s="6">
-        <v>3680</v>
-      </c>
-      <c r="J16" s="6">
-        <v>692</v>
-      </c>
-      <c r="K16" s="6">
-        <v>3680</v>
-      </c>
-      <c r="L16" s="6">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="6">
-        <v>265</v>
-      </c>
-      <c r="D17" s="6">
-        <v>50</v>
-      </c>
-      <c r="E17" s="6">
-        <v>530</v>
-      </c>
-      <c r="F17" s="6">
-        <v>100</v>
-      </c>
-      <c r="G17" s="6">
-        <v>265</v>
-      </c>
-      <c r="H17" s="6">
-        <v>50</v>
-      </c>
-      <c r="I17" s="6">
-        <v>530</v>
-      </c>
-      <c r="J17" s="6">
-        <v>100</v>
-      </c>
-      <c r="K17" s="6">
-        <v>530</v>
-      </c>
-      <c r="L17" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="6">
-        <v>1840</v>
-      </c>
-      <c r="D18" s="6">
-        <v>346</v>
-      </c>
-      <c r="E18" s="6">
-        <v>3680</v>
-      </c>
-      <c r="F18" s="6">
-        <v>692</v>
-      </c>
-      <c r="G18" s="6">
-        <v>1840</v>
-      </c>
-      <c r="H18" s="6">
-        <v>346</v>
-      </c>
-      <c r="I18" s="6">
-        <v>3680</v>
-      </c>
-      <c r="J18" s="6">
-        <v>692</v>
-      </c>
-      <c r="K18" s="6">
-        <v>3680</v>
-      </c>
-      <c r="L18" s="6">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="6">
-        <v>168</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6">
-        <v>335</v>
-      </c>
-      <c r="F19" s="6">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6">
-        <v>168</v>
-      </c>
-      <c r="H19" s="6">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6">
-        <v>335</v>
-      </c>
-      <c r="J19" s="6">
-        <v>0</v>
-      </c>
-      <c r="K19" s="6">
-        <v>335</v>
-      </c>
-      <c r="L19" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="6">
-        <v>0</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6">
-        <v>0</v>
-      </c>
-      <c r="J20" s="6">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6">
-        <v>0</v>
-      </c>
-      <c r="L20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="6">
-        <v>168</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <v>335</v>
-      </c>
-      <c r="F21" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
-        <v>168</v>
-      </c>
-      <c r="H21" s="6">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6">
-        <v>335</v>
-      </c>
-      <c r="J21" s="6">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
-        <v>335</v>
-      </c>
-      <c r="L21" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="6">
-        <v>168</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>335</v>
-      </c>
-      <c r="F22" s="6">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
-        <v>168</v>
-      </c>
-      <c r="H22" s="6">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6">
-        <v>335</v>
-      </c>
-      <c r="J22" s="6">
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
-        <v>335</v>
-      </c>
-      <c r="L22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="6">
-        <v>168</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6">
-        <v>335</v>
-      </c>
-      <c r="F23" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
-        <v>168</v>
-      </c>
-      <c r="H23" s="6">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <v>335</v>
-      </c>
-      <c r="J23" s="6">
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
-        <v>335</v>
-      </c>
-      <c r="L23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="6">
-        <v>110</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6">
-        <v>220</v>
-      </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6">
-        <v>110</v>
-      </c>
-      <c r="H24" s="6">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6">
-        <v>220</v>
-      </c>
-      <c r="J24" s="6">
-        <v>0</v>
-      </c>
-      <c r="K24" s="6">
-        <v>220</v>
-      </c>
-      <c r="L24" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="6">
-        <v>0</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6">
-        <v>0</v>
-      </c>
-      <c r="J25" s="6">
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
-        <v>0</v>
-      </c>
-      <c r="L25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="6">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6">
-        <v>0</v>
-      </c>
-      <c r="K26" s="6">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="6">
-        <v>0</v>
-      </c>
-      <c r="D27" s="6">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6">
-        <v>0</v>
-      </c>
-      <c r="J27" s="6">
-        <v>0</v>
-      </c>
-      <c r="K27" s="6">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="6">
-        <v>0</v>
-      </c>
-      <c r="D28" s="6">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6">
-        <v>0</v>
-      </c>
-      <c r="K28" s="6">
-        <v>0</v>
-      </c>
-      <c r="L28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="6">
-        <v>0</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0</v>
-      </c>
-      <c r="F29" s="6">
-        <v>0</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0</v>
-      </c>
-      <c r="H29" s="6">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6">
-        <v>0</v>
-      </c>
-      <c r="J29" s="6">
-        <v>0</v>
-      </c>
-      <c r="K29" s="6">
-        <v>0</v>
-      </c>
-      <c r="L29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="6">
-        <v>0</v>
-      </c>
-      <c r="D30" s="6">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6">
-        <v>0</v>
-      </c>
-      <c r="G30" s="6">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6">
-        <v>0</v>
-      </c>
-      <c r="J30" s="6">
-        <v>0</v>
-      </c>
-      <c r="K30" s="6">
-        <v>0</v>
-      </c>
-      <c r="L30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="6">
-        <v>0</v>
-      </c>
-      <c r="D31" s="6">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0</v>
-      </c>
-      <c r="H31" s="6">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6">
-        <v>0</v>
-      </c>
-      <c r="J31" s="6">
-        <v>0</v>
-      </c>
-      <c r="K31" s="6">
-        <v>0</v>
-      </c>
-      <c r="L31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="6">
-        <v>0</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0</v>
-      </c>
-      <c r="G32" s="6">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6">
-        <v>0</v>
-      </c>
-      <c r="I32" s="6">
-        <v>0</v>
-      </c>
-      <c r="J32" s="6">
-        <v>0</v>
-      </c>
-      <c r="K32" s="6">
-        <v>0</v>
-      </c>
-      <c r="L32" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="6">
-        <v>0</v>
-      </c>
-      <c r="D33" s="6">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6">
-        <v>0</v>
-      </c>
-      <c r="J33" s="6">
-        <v>0</v>
-      </c>
-      <c r="K33" s="6">
-        <v>0</v>
-      </c>
-      <c r="L33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="6">
-        <v>0</v>
-      </c>
-      <c r="D34" s="6">
-        <v>0</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0</v>
-      </c>
-      <c r="F34" s="6">
-        <v>0</v>
-      </c>
-      <c r="G34" s="6">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6">
-        <v>0</v>
-      </c>
-      <c r="J34" s="6">
-        <v>0</v>
-      </c>
-      <c r="K34" s="6">
-        <v>0</v>
-      </c>
-      <c r="L34" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C35" s="6">
-        <v>168</v>
-      </c>
-      <c r="D35" s="6">
-        <v>0</v>
-      </c>
-      <c r="E35" s="6">
-        <v>335</v>
-      </c>
-      <c r="F35" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="6">
-        <v>168</v>
-      </c>
-      <c r="H35" s="6">
-        <v>0</v>
-      </c>
-      <c r="I35" s="6">
-        <v>335</v>
-      </c>
-      <c r="J35" s="6">
-        <v>0</v>
-      </c>
-      <c r="K35" s="6">
-        <v>335</v>
-      </c>
-      <c r="L35" s="6">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>